--- a/DEMOQA/Testdata/Elements.xlsx
+++ b/DEMOQA/Testdata/Elements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8000" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="18350" windowHeight="8000" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Text Box" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>Full Name</t>
   </si>
@@ -164,6 +164,12 @@
   </si>
   <si>
     <t>Broken Link</t>
+  </si>
+  <si>
+    <t>File Name</t>
+  </si>
+  <si>
+    <t>Automation-Testing.jpg</t>
   </si>
 </sst>
 </file>
@@ -1940,9 +1946,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
-  <sheetData/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="1"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
